--- a/jogos_2024-09-24.xlsx
+++ b/jogos_2024-09-24.xlsx
@@ -643,75 +643,75 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA2" t="n">
         <v>3.4</v>
@@ -720,14 +720,14 @@
         <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['86', '89']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AH2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
       </c>
-      <c r="AI2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45559.3125</v>
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,49 +927,49 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
         <v>3.4</v>
@@ -978,14 +978,14 @@
         <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['86', '89']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45559.3125</v>
@@ -2181,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>1.64</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
         <v>1.53</v>
       </c>
       <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['10', '57']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>1.03</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['28', '36', '77']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>4.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.8</v>
+        <v>3.48</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45559.5625</v>
@@ -2439,33 +2439,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
@@ -2475,65 +2475,65 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.199999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
         <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>3.94</v>
+        <v>4.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.36</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['10', '57']</t>
+          <t>['28', '36', '77']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.48</v>
+        <v>1.8</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45559.5625</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,91 +2578,91 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.21</v>
-      </c>
       <c r="Q17" t="n">
-        <v>2.46</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="X17" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="Y17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['13', '31', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.66</v>
+        <v>2.63</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45559.58333333334</v>
@@ -2697,32 +2697,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.45</v>
+        <v>2.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['45', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45559.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,23 +2836,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yeni Malatyaspor</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.46</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['25', '58']</t>
+          <t>['13', '31', '68']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3120,28 +3120,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
         <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.5</v>
@@ -3150,53 +3150,53 @@
         <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.86</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['45', '85']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.1</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="AI22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.88</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sandhausen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unterhaching</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
         <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>3.24</v>
       </c>
       <c r="P23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['15', '60', '64', '78']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['19', '53', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2</v>
       </c>
-      <c r="AA23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['28', '34', '66', '90+6']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>1.53</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>7.5</v>
       </c>
       <c r="R24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.36</v>
       </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>['11', '78']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3600,26 +3600,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.6</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['13', '17', '76', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>3.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['11', '33']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Yeni Malatyaspor</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['25', '58']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3858,119 +3858,119 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.5</v>
+        <v>3.95</v>
       </c>
       <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.62</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['11', '78']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45559.58333333334</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandhausen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Unterhaching</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>3.24</v>
+        <v>2.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.78</v>
+        <v>4.33</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['28', '34', '66', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.15</v>
       </c>
-      <c r="X28" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AH28" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['15', '60', '64', '78']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['19', '53', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45559.58333333334</v>
@@ -4116,26 +4116,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>7</v>
+        <v>2.43</v>
       </c>
       <c r="O29" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['13', '17', '76', '90+1']</t>
+          <t>['11', '33']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.34</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45559.58333333334</v>
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O34" t="n">
         <v>2</v>
       </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.28</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['65', '83']</t>
+          <t>['35', '37', '45+3', '48', '70', '81']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45559.64583333334</v>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,43 +4926,43 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>2.06</v>
       </c>
       <c r="M35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q35" t="n">
         <v>4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>7</v>
       </c>
       <c r="R35" t="n">
         <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y35" t="n">
         <v>1.9</v>
@@ -4971,38 +4971,38 @@
         <v>1.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['35', '37', '45+3', '48', '70', '81']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH35" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ35" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5029,16 +5029,16 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -5047,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="M36" t="n">
         <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T36" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['13', '81']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['27', '70', '79', '83']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.73</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['28', '82', '85']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="P38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['76', '83', '85']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.25</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['58', '71']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['27', '70', '79', '83']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5545,109 +5545,109 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P40" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['65', '83']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.48</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['10', '75']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N41" t="n">
         <v>3</v>
       </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O41" t="n">
+        <v>3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y41" t="n">
         <v>2.55</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['58', '71']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.91</v>
       </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['76', '83', '85']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ41" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="O42" t="n">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="P42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z42" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="AA42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['28', '82', '85']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH42" t="n">
         <v>2.65</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['13', '81']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI42" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45559.64583333334</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,22 +5958,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="O43" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -5982,41 +5982,41 @@
         <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="U43" t="n">
         <v>1.44</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="X43" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD43" t="n">
         <v>2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45559.64583333334</v>
@@ -6061,16 +6061,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -6087,65 +6087,65 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.6</v>
+        <v>2.17</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="T44" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="X44" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['10', '75']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI44" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45559.64583333334</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,109 +6190,109 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M45" t="n">
         <v>3</v>
       </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M45" t="n">
-        <v>4.7</v>
-      </c>
       <c r="N45" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="P45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y45" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q45" t="n">
-        <v>6</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['18', '90+9']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['46', '54', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45559.65625</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="T46" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="X46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA46" t="n">
         <v>4.33</v>
       </c>
-      <c r="Y46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AC46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD46" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['30', '89']</t>
         </is>
       </c>
       <c r="AG46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.18</v>
       </c>
-      <c r="AH46" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AI46" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45559.65625</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['35', '89']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>2.6</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>2.45</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45559.65625</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="M48" t="n">
-        <v>5.49</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>9.92</v>
+        <v>2.38</v>
       </c>
       <c r="O48" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="P48" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="R48" t="n">
         <v>1.32</v>
       </c>
       <c r="S48" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="U48" t="n">
         <v>1.48</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X48" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AB48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['20', '53']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['42', '45+1']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['6', '87']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['12', '90+2', '90+8']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AJ48" t="n">
-        <v>4.1</v>
+        <v>1.88</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45559.65625</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N49" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T49" t="n">
         <v>2.6</v>
       </c>
-      <c r="O49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P49" t="n">
+      <c r="U49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z49" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['31', '45+6']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI49" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ49" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45559.65625</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Taranto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N51" t="n">
+        <v>9</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.5</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['62', '78']</t>
+          <t>['48', '58', '66', '90+7']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AJ51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45559.65625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Loughgall</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7119,65 +7119,65 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="M52" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="N52" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.62</v>
       </c>
-      <c r="P52" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>9</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X52" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.56</v>
-      </c>
       <c r="AA52" t="n">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['14', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AH52" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ52" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45559.65625</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Turris Neapolis</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N53" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="P53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X53" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R53" t="n">
+      <c r="AA53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI53" t="n">
         <v>1.5</v>
       </c>
-      <c r="S53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AJ53" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45559.65625</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,87 +7351,87 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Turris Neapolis</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O54" t="n">
+        <v>6</v>
+      </c>
+      <c r="P54" t="n">
         <v>2</v>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q54" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="R54" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S54" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="T54" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="V54" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W54" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="X54" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7440,20 +7440,20 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['31', '45+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.82</v>
+        <v>1.12</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45559.65625</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,109 +7480,109 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>13</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>11</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T55" t="n">
         <v>2</v>
       </c>
-      <c r="H55" t="n">
+      <c r="U55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA55" t="n">
         <v>2</v>
       </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V55" t="n">
+      <c r="AB55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
         <v>1.03</v>
       </c>
-      <c r="W55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['20', '53']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['42', '45+1']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH55" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="AI55" t="n">
-        <v>2</v>
+        <v>1.16</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.88</v>
+        <v>4.8</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45559.65625</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="M56" t="n">
         <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S56" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T56" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="U56" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="V56" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.5</v>
       </c>
-      <c r="X56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['35', '89']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI56" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45559.65625</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
         <v>1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.33</v>
+        <v>1.26</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>5.49</v>
       </c>
       <c r="N57" t="n">
-        <v>1.75</v>
+        <v>9.92</v>
       </c>
       <c r="O57" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S57" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="T57" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['6', '87']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>['12', '90+2', '90+8']</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH57" t="n">
         <v>3.2</v>
       </c>
-      <c r="U57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>['30', '89']</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI57" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.53</v>
+        <v>4.1</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45559.65625</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.21</v>
+        <v>1.48</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="N58" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="O58" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S58" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="T58" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="U58" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="V58" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W58" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X58" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="Y58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '90+9']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '54', '58']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45559.65625</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,22 +7996,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="M59" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="O59" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="P59" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>8.5</v>
+        <v>4.33</v>
       </c>
       <c r="R59" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S59" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="T59" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U59" t="n">
         <v>1.35</v>
       </c>
       <c r="V59" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W59" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X59" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['48', '58', '66', '90+7']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AJ59" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45559.65625</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,16 +8125,16 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Taranto</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N60" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y60" t="n">
         <v>2.15</v>
       </c>
-      <c r="M60" t="n">
-        <v>3</v>
-      </c>
-      <c r="N60" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O60" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q60" t="n">
+      <c r="Z60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>['62', '78']</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ60" t="n">
         <v>4</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X60" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45559.65625</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,23 +8254,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Loughgall</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>1</v>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="M61" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R61" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S61" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="U61" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="V61" t="n">
         <v>1.01</v>
       </c>
       <c r="W61" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X61" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AA61" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
+          <t>['14', '81']</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
       <c r="AG61" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AH61" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AJ61" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45559.65625</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,25 +8383,25 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8409,55 +8409,55 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>5.9</v>
+        <v>1.22</v>
       </c>
       <c r="M62" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="N62" t="n">
-        <v>1.44</v>
+        <v>12</v>
       </c>
       <c r="O62" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="P62" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.1</v>
+        <v>9.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S62" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="T62" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U62" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="V62" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W62" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="X62" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AC62" t="n">
         <v>2.1</v>
@@ -8467,25 +8467,25 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['1', '40', '48']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>['22', '54']</t>
+          <t>['85', '86']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="AI62" t="n">
-        <v>3</v>
+        <v>1.17</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.45</v>
+        <v>5</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45559.66666666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,25 +8512,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8538,55 +8538,55 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.22</v>
+        <v>5.9</v>
       </c>
       <c r="M63" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="N63" t="n">
-        <v>12</v>
+        <v>1.44</v>
       </c>
       <c r="O63" t="n">
-        <v>1.62</v>
+        <v>6</v>
       </c>
       <c r="P63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S63" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q63" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S63" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T63" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U63" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="V63" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W63" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="X63" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AC63" t="n">
         <v>2.1</v>
@@ -8596,25 +8596,25 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['1', '40', '48']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['85', '86']</t>
+          <t>['22', '54']</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="n">
-        <v>4.5</v>
+        <v>1.07</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.17</v>
+        <v>3</v>
       </c>
       <c r="AJ63" t="n">
-        <v>5</v>
+        <v>1.45</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45559.66666666666</v>
@@ -8899,109 +8899,109 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>2</v>
       </c>
       <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="M66" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>6.75</v>
+        <v>2.95</v>
       </c>
       <c r="O66" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="P66" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="R66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U66" t="n">
         <v>1.33</v>
       </c>
-      <c r="S66" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V66" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X66" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y66" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z66" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z66" t="n">
-        <v>2</v>
-      </c>
       <c r="AA66" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AC66" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>['18', '88']</t>
+          <t>['88', '90+8']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['22', '61']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AH66" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45559.83333333334</v>
@@ -9028,109 +9028,109 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>2</v>
       </c>
       <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N67" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>7</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X67" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z67" t="n">
         <v>2</v>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M67" t="n">
+      <c r="AA67" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>['18', '88']</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH67" t="n">
         <v>3</v>
       </c>
-      <c r="N67" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W67" t="n">
+      <c r="AI67" t="n">
         <v>1.29</v>
       </c>
-      <c r="X67" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>['88', '90+8']</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['22', '61']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45559.83333333334</v>
